--- a/AAII_Financials/Quarterly/AFCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFCG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
   <si>
     <t>AFCG</t>
   </si>
@@ -656,237 +656,249 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E8" s="3">
         <v>14100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>16100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>16800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>19700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>18100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>19900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>17400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>11000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1600</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E9" s="3">
         <v>3600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>100</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E10" s="3">
         <v>10500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>15800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>14300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>15700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>13600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6600</v>
-      </c>
-      <c r="N10" s="3">
-        <v>3800</v>
       </c>
       <c r="O10" s="3">
         <v>3800</v>
       </c>
       <c r="P10" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Q10" s="3">
         <v>1500</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,8 +917,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -955,8 +968,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,8 +1021,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1017,11 +1036,11 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-2000</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1037,8 +1056,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1055,8 +1074,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1105,8 +1127,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,108 +1147,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E17" s="3">
         <v>5200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1100</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E18" s="3">
         <v>8900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>11200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>12400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>13800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>12800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>14100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>11000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>500</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,88 +1274,92 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-10200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1600</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E21" s="3">
         <v>8600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>12300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>10200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>11600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>11500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>10200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7100</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1342,8 +1378,11 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1392,58 +1431,64 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E23" s="3">
         <v>8600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>12300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>10200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>11600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>11500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>10200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2100</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1451,31 +1496,31 @@
         <v>700</v>
       </c>
       <c r="E24" s="3">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="F24" s="3">
         <v>200</v>
       </c>
       <c r="G24" s="3">
+        <v>200</v>
+      </c>
+      <c r="H24" s="3">
         <v>700</v>
-      </c>
-      <c r="H24" s="3">
-        <v>200</v>
       </c>
       <c r="I24" s="3">
         <v>200</v>
       </c>
       <c r="J24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1492,8 +1537,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,108 +1590,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E26" s="3">
         <v>8000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>12100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>10000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>11500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>11400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2100</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E27" s="3">
         <v>8000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>12100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>10000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>11500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>11400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>10200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2100</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1749,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1742,8 +1802,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1855,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,108 +1908,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>10200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E33" s="3">
         <v>8000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>12100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>10000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>11500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>11400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>10200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2100</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,113 +2067,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E35" s="3">
         <v>8000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>12100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>10000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>11500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>11400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>10200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2100</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2201,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,58 +2222,62 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>121600</v>
+      </c>
+      <c r="E41" s="3">
         <v>73200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>82100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>80600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>140400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>36300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>45600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>63600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>109200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>70000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>124600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>126800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>31200</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2237,31 +2326,34 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>1800</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2281,14 +2373,17 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
+      <c r="Q43" s="3">
+        <v>0</v>
       </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2337,25 +2432,28 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>700</v>
+      </c>
+      <c r="E45" s="3">
         <v>500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>600</v>
       </c>
       <c r="I45" s="3">
         <v>600</v>
@@ -2364,31 +2462,34 @@
         <v>600</v>
       </c>
       <c r="K45" s="3">
+        <v>600</v>
+      </c>
+      <c r="L45" s="3">
         <v>900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>800</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2429,66 +2530,72 @@
         <v>0</v>
       </c>
       <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3">
         <v>32100</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>342400</v>
+      </c>
+      <c r="E47" s="3">
         <v>370400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>371200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>366800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>378300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>434400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>413100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>389800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>354700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>233500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>153700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>93600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>84300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>50700</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2537,8 +2644,11 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2587,8 +2697,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2750,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,8 +2803,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2737,8 +2856,11 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,58 +2909,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>466600</v>
+      </c>
+      <c r="E54" s="3">
         <v>445100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>454000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>447800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>519200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>471300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>459300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>454100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>464800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>303900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>278500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>221500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>94000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>82700</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2985,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,58 +3006,62 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>700</v>
+      </c>
+      <c r="E57" s="3">
         <v>800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2977,58 +3110,64 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>57700</v>
+      </c>
+      <c r="E59" s="3">
         <v>17500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>24400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>20200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>81400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>25100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>22700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>18700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>93000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>28300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1700</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3069,46 +3208,49 @@
         <v>0</v>
       </c>
       <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3">
         <v>1900</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>88000</v>
+      </c>
+      <c r="E61" s="3">
         <v>87900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>87700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>87600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>97100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>97000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>96800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>96700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>96600</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3127,58 +3269,64 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>100</v>
+      </c>
+      <c r="E62" s="3">
         <v>200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>600</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>300</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3375,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3428,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,58 +3481,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>146500</v>
+      </c>
+      <c r="E66" s="3">
         <v>106300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>113700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>110000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>180100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>123900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>121100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>117600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>191800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>29500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1900</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3557,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3608,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3661,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3547,8 +3714,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,58 +3767,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-10900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-9100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-11400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-10000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2100</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3873,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3926,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,58 +3979,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>320100</v>
+      </c>
+      <c r="E76" s="3">
         <v>338800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>340300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>337900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>339100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>347400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>338200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>336500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>273100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>274400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>268500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>216300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>91600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>80900</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,113 +4085,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E81" s="3">
         <v>8000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>12100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>10000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>11500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>11400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>10200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2100</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,8 +4219,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4072,8 +4270,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4323,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4376,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4429,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4482,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,58 +4535,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E89" s="3">
         <v>5500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>12200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>10600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-100</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,8 +4611,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4442,8 +4662,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4715,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,58 +4768,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>8000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>15000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>52200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-19400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-19100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-30000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-127000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-59800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-54800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-31800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-600</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,8 +4844,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4621,38 +4854,38 @@
         <v>-9800</v>
       </c>
       <c r="E96" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="F96" s="3">
         <v>-11500</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-11400</v>
       </c>
       <c r="G96" s="3">
         <v>-11400</v>
       </c>
       <c r="H96" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="I96" s="3">
         <v>-11100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-10900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-8200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-7100</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-5100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2200</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
@@ -4662,8 +4895,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4948,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5001,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,58 +5054,64 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-11700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-79100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>48000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-9500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-20200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>164300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>5000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>47500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>121700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>8600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>31900</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4912,54 +5160,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-59800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>104100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-18000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-45600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>39300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-54600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>117200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-21600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>31200</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AFCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFCG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
   <si>
     <t>AFCG</t>
   </si>
@@ -656,143 +656,150 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E8" s="3">
         <v>15900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>16100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>16800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>19700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>18100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>17400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1600</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -800,105 +807,111 @@
         <v>3500</v>
       </c>
       <c r="E9" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F9" s="3">
         <v>3600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>100</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E10" s="3">
         <v>12400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>13100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>15800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>14300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>15700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>13600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6600</v>
-      </c>
-      <c r="O10" s="3">
-        <v>3800</v>
       </c>
       <c r="P10" s="3">
         <v>3800</v>
       </c>
       <c r="Q10" s="3">
+        <v>3800</v>
+      </c>
+      <c r="R10" s="3">
         <v>1500</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,8 +931,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -971,8 +985,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1024,8 +1041,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1039,11 +1059,11 @@
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>-2000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1059,8 +1079,8 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1077,8 +1097,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1130,8 +1153,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1148,114 +1174,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E17" s="3">
         <v>5100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1100</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E18" s="3">
         <v>10800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>8900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>11200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>12400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>13800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>12800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>14100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>11000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>500</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1275,94 +1308,98 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-19400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-10200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1600</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-8500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>8600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>12300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>10200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>11600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>11500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7100</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1381,8 +1418,11 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1434,96 +1474,102 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>8600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>12300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>10200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>11600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>11500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>10200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2100</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
         <v>700</v>
       </c>
       <c r="F24" s="3">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="G24" s="3">
         <v>200</v>
       </c>
       <c r="H24" s="3">
+        <v>200</v>
+      </c>
+      <c r="I24" s="3">
         <v>700</v>
-      </c>
-      <c r="I24" s="3">
-        <v>200</v>
       </c>
       <c r="J24" s="3">
         <v>200</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -1540,8 +1586,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1593,114 +1642,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>12100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>10000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>11500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>11400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2100</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>12100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>10000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>11500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>11400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>10200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2100</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1752,8 +1810,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1805,8 +1866,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1858,8 +1922,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1911,114 +1978,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E32" s="3">
         <v>19400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>10200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1600</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>12100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>11500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>11400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>10200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2100</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2070,119 +2146,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>12100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>10000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>11500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>11400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>10200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2100</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2202,8 +2287,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2223,61 +2309,65 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>82300</v>
+      </c>
+      <c r="E41" s="3">
         <v>121600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>73200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>82100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>80600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>140400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>36300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>45600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>63600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>109200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>70000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>124600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>126800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>31200</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2329,17 +2419,20 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1800</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2355,8 +2448,8 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2376,14 +2469,17 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
+      <c r="R43" s="3">
+        <v>0</v>
       </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2435,28 +2531,31 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>500</v>
+      </c>
+      <c r="E45" s="3">
         <v>700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>600</v>
       </c>
       <c r="J45" s="3">
         <v>600</v>
@@ -2465,31 +2564,34 @@
         <v>600</v>
       </c>
       <c r="L45" s="3">
+        <v>600</v>
+      </c>
+      <c r="M45" s="3">
         <v>900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>800</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2533,69 +2635,75 @@
         <v>0</v>
       </c>
       <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3">
         <v>32100</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>387900</v>
+      </c>
+      <c r="E47" s="3">
         <v>342400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>370400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>371200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>366800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>378300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>434400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>413100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>389800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>354700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>233500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>153700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>93600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>84300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>50700</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2647,8 +2755,11 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2700,8 +2811,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2753,8 +2867,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2806,8 +2923,11 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2859,8 +2979,11 @@
       <c r="S52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2912,61 +3035,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>476400</v>
+      </c>
+      <c r="E54" s="3">
         <v>466600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>445100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>454000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>447800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>519200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>471300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>459300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>454100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>464800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>303900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>278500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>221500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>94000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>82700</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2986,8 +3115,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3007,61 +3137,65 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E57" s="3">
         <v>700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>100</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3113,61 +3247,67 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>76600</v>
+      </c>
+      <c r="E59" s="3">
         <v>57700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>17500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>24400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>20200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>81400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>25100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>22700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>18700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>93000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>28300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1700</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3211,49 +3351,52 @@
         <v>0</v>
       </c>
       <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3">
         <v>1900</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>88200</v>
+      </c>
+      <c r="E61" s="3">
         <v>88000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>87900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>87700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>87600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>97100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>97000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>96800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>96700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>96600</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3272,61 +3415,67 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
         <v>100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>600</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
         <v>700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>300</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3378,8 +3527,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3431,8 +3583,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3484,61 +3639,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>165800</v>
+      </c>
+      <c r="E66" s="3">
         <v>146500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>106300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>113700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>110000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>180100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>123900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>121100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>117600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>191800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>29500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1900</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3558,8 +3719,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3611,8 +3773,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3664,8 +3829,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3717,8 +3885,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3770,61 +3941,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-39900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-30000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-10900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-9100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-11400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-10000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2100</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3876,8 +4053,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3929,8 +4109,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3982,61 +4165,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>310600</v>
+      </c>
+      <c r="E76" s="3">
         <v>320100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>338800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>340300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>337900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>339100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>347400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>338200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>336500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>273100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>274400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>268500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>216300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>91600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>80900</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4088,119 +4277,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>12100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>10000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>11500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>11400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>10200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2100</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4220,8 +4418,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4273,8 +4472,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4326,8 +4528,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4379,8 +4584,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4432,8 +4640,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4485,8 +4696,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4538,61 +4752,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E89" s="3">
         <v>6200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>12200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-100</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4612,8 +4832,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4665,8 +4886,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4718,8 +4942,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4771,61 +4998,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-53900</v>
+      </c>
+      <c r="E94" s="3">
         <v>10000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>8000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>15000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>52200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-19400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-19100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-30000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-127000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-59800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-54800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-31800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-600</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4845,8 +5078,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4857,38 +5091,38 @@
         <v>-9800</v>
       </c>
       <c r="F96" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="G96" s="3">
         <v>-11500</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-11400</v>
       </c>
       <c r="H96" s="3">
         <v>-11400</v>
       </c>
       <c r="I96" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="J96" s="3">
         <v>-11100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-10900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-8200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-7100</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-5100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2200</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -4898,8 +5132,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4951,8 +5188,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5004,8 +5244,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5057,61 +5300,67 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E100" s="3">
         <v>32200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-9800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-11700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-79100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>48000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-9500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-20200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>164300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>5000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>47500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>121700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>8600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>31900</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5163,57 +5412,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-39300</v>
+      </c>
+      <c r="E102" s="3">
         <v>48400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-59800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>104100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-18000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-45600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>39300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-54600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>117200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-21600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>31200</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AFCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFCG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
   <si>
     <t>AFCG</t>
   </si>
@@ -656,262 +656,275 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E8" s="3">
         <v>14700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>16100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>16800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>19700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>18100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1600</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="E9" s="3">
         <v>3500</v>
       </c>
       <c r="F9" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G9" s="3">
         <v>3600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>100</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E10" s="3">
         <v>11200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>10500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>12800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>13100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>15800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>14300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>15700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>13600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>10200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6600</v>
-      </c>
-      <c r="P10" s="3">
-        <v>3800</v>
       </c>
       <c r="Q10" s="3">
         <v>3800</v>
       </c>
       <c r="R10" s="3">
+        <v>3800</v>
+      </c>
+      <c r="S10" s="3">
         <v>1500</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -932,8 +945,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -988,8 +1002,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1044,8 +1061,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1062,11 +1082,11 @@
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>-2000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1082,8 +1102,8 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1100,8 +1120,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1156,8 +1179,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1175,120 +1201,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E17" s="3">
         <v>6000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1100</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E18" s="3">
         <v>8700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>10800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>8900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>11200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>12400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>13800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>12800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>14100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>500</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1309,100 +1342,104 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-8600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-19400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-10200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1600</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E21" s="3">
         <v>100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-8500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>12300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>10200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>11600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>11500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>10200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7100</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1421,8 +1458,11 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1477,102 +1517,108 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E23" s="3">
         <v>100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>8600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>12300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>10200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>11600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>11500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>10200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2100</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
-      </c>
-      <c r="E24" s="3">
-        <v>700</v>
       </c>
       <c r="F24" s="3">
         <v>700</v>
       </c>
       <c r="G24" s="3">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="H24" s="3">
         <v>200</v>
       </c>
       <c r="I24" s="3">
+        <v>200</v>
+      </c>
+      <c r="J24" s="3">
         <v>700</v>
-      </c>
-      <c r="J24" s="3">
-        <v>200</v>
       </c>
       <c r="K24" s="3">
         <v>200</v>
       </c>
       <c r="L24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1589,8 +1635,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1645,120 +1694,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>12100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>10000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>11500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>11400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2100</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>12100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>10000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>11500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>11400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>10200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2100</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1813,8 +1871,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1869,8 +1930,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1925,8 +1989,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1981,120 +2048,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E32" s="3">
         <v>8600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>19400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>10200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1600</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>12100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>10000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>11500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>11400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>10200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2100</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2149,125 +2225,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>12100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>10000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>11500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>11400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>10200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2100</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2288,8 +2373,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2310,64 +2396,68 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>170300</v>
+      </c>
+      <c r="E41" s="3">
         <v>82300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>121600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>73200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>82100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>80600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>140400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>36300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>45600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>63600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>109200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>70000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>124600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>126800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>31200</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2422,20 +2512,23 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
         <v>5700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1800</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2451,8 +2544,8 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2472,14 +2565,17 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
+      <c r="S43" s="3">
+        <v>0</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2534,31 +2630,34 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>700</v>
+      </c>
+      <c r="E45" s="3">
         <v>500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>500</v>
-      </c>
-      <c r="J45" s="3">
-        <v>600</v>
       </c>
       <c r="K45" s="3">
         <v>600</v>
@@ -2567,31 +2666,34 @@
         <v>600</v>
       </c>
       <c r="M45" s="3">
+        <v>600</v>
+      </c>
+      <c r="N45" s="3">
         <v>900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>800</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2638,72 +2740,78 @@
         <v>0</v>
       </c>
       <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3">
         <v>32100</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>287000</v>
+      </c>
+      <c r="E47" s="3">
         <v>387900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>342400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>370400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>371200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>366800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>378300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>434400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>413100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>389800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>354700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>233500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>153700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>93600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>84300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>50700</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2758,8 +2866,11 @@
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2814,8 +2925,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2870,8 +2984,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2926,8 +3043,11 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2982,8 +3102,11 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3038,64 +3161,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>458000</v>
+      </c>
+      <c r="E54" s="3">
         <v>476400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>466600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>445100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>454000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>447800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>519200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>471300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>459300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>454100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>464800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>303900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>278500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>221500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>94000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>82700</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3116,8 +3245,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3138,64 +3268,68 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>100</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3250,64 +3384,70 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>53800</v>
+      </c>
+      <c r="E59" s="3">
         <v>76600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>57700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>17500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>24400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>20200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>81400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>25100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>22700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>93000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>28300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1700</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3354,52 +3494,55 @@
         <v>0</v>
       </c>
       <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3">
         <v>1900</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>88300</v>
+      </c>
+      <c r="E61" s="3">
         <v>88200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>88000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>87900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>87700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>87600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>97100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>97000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>96800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>96700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>96600</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3418,64 +3561,70 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
         <v>100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>600</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3">
         <v>700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>300</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3530,8 +3679,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3586,8 +3738,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3642,64 +3797,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>143700</v>
+      </c>
+      <c r="E66" s="3">
         <v>165800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>146500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>106300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>113700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>110000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>180100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>123900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>121100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>117600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>191800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>29500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1900</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3720,8 +3881,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3776,8 +3938,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3832,8 +3997,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3888,8 +4056,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3944,64 +4115,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-36500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-39900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-30000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-10900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-9100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-11400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-10000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2100</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4056,8 +4233,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4112,8 +4292,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4168,64 +4351,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>314300</v>
+      </c>
+      <c r="E76" s="3">
         <v>310600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>320100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>338800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>340300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>337900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>339100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>347400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>338200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>336500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>273100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>274400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>268500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>216300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>91600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>80900</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4280,125 +4469,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>12100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>10000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>11500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>11400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>10200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2100</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4419,8 +4617,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4475,8 +4674,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4531,8 +4733,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4587,8 +4792,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4643,8 +4851,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4699,8 +4910,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4755,64 +4969,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E89" s="3">
         <v>6400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>12200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>10600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-100</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4833,8 +5053,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4889,8 +5110,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4945,8 +5169,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5001,64 +5228,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>113000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-53900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>10000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>8000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>15000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>52200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-19400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-19100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-30000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-127000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-59800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-54800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-31800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-600</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5079,13 +5312,14 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-9800</v>
+        <v>-9900</v>
       </c>
       <c r="E96" s="3">
         <v>-9800</v>
@@ -5094,38 +5328,38 @@
         <v>-9800</v>
       </c>
       <c r="G96" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="H96" s="3">
         <v>-11500</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-11400</v>
       </c>
       <c r="I96" s="3">
         <v>-11400</v>
       </c>
       <c r="J96" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="K96" s="3">
         <v>-11100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-10900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-8200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-7100</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-5100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -5135,8 +5369,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5191,8 +5428,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5247,8 +5487,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5303,64 +5546,70 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-35300</v>
+      </c>
+      <c r="E100" s="3">
         <v>8200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>32200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-9800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-11700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-79100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>48000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-20200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>164300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>5000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>47500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>121700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>8600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>31900</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5415,60 +5664,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>88000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-39300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>48400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-8900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-59800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>104100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-9300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-18000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-45600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>39300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-54600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>117200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-21600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>31200</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AFCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFCG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
   <si>
     <t>AFCG</t>
   </si>
@@ -656,275 +656,288 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>18400</v>
-      </c>
-      <c r="E8" s="3">
-        <v>14700</v>
+        <v>8700</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F8" s="3">
-        <v>15900</v>
+        <v>9800</v>
       </c>
       <c r="G8" s="3">
-        <v>14100</v>
+        <v>4000</v>
       </c>
       <c r="H8" s="3">
+        <v>14200</v>
+      </c>
+      <c r="I8" s="3">
+        <v>17700</v>
+      </c>
+      <c r="J8" s="3">
         <v>16100</v>
       </c>
-      <c r="I8" s="3">
-        <v>16800</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>18100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1600</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
-        <v>4000</v>
-      </c>
-      <c r="E9" s="3">
-        <v>3500</v>
-      </c>
-      <c r="F9" s="3">
-        <v>3500</v>
-      </c>
-      <c r="G9" s="3">
-        <v>3600</v>
-      </c>
-      <c r="H9" s="3">
-        <v>3300</v>
-      </c>
-      <c r="I9" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" s="3">
         <v>3900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>100</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>14400</v>
-      </c>
-      <c r="E10" s="3">
-        <v>11200</v>
+        <v>8700</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F10" s="3">
-        <v>12400</v>
+        <v>9800</v>
       </c>
       <c r="G10" s="3">
-        <v>10500</v>
+        <v>4000</v>
       </c>
       <c r="H10" s="3">
-        <v>12800</v>
+        <v>14200</v>
       </c>
       <c r="I10" s="3">
-        <v>13100</v>
+        <v>17700</v>
       </c>
       <c r="J10" s="3">
+        <v>16100</v>
+      </c>
+      <c r="K10" s="3">
         <v>15800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>14300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>15700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>13600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>10200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6600</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>3800</v>
       </c>
       <c r="R10" s="3">
         <v>3800</v>
       </c>
       <c r="S10" s="3">
+        <v>3800</v>
+      </c>
+      <c r="T10" s="3">
         <v>1500</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -946,8 +959,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1005,8 +1019,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,31 +1081,34 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+        <v>1200</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-1300</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -1105,8 +1125,8 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1123,8 +1143,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1182,8 +1205,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,126 +1228,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="3">
+        <v>5500</v>
+      </c>
+      <c r="G17" s="3">
+        <v>4400</v>
+      </c>
+      <c r="H17" s="3">
+        <v>5200</v>
+      </c>
+      <c r="I17" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J17" s="3">
+        <v>5700</v>
+      </c>
+      <c r="K17" s="3">
+        <v>5900</v>
+      </c>
+      <c r="L17" s="3">
+        <v>5300</v>
+      </c>
+      <c r="M17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="N17" s="3">
         <v>6400</v>
       </c>
-      <c r="E17" s="3">
-        <v>6000</v>
-      </c>
-      <c r="F17" s="3">
-        <v>5100</v>
-      </c>
-      <c r="G17" s="3">
-        <v>5200</v>
-      </c>
-      <c r="H17" s="3">
-        <v>4900</v>
-      </c>
-      <c r="I17" s="3">
-        <v>4400</v>
-      </c>
-      <c r="J17" s="3">
-        <v>5900</v>
-      </c>
-      <c r="K17" s="3">
-        <v>5300</v>
-      </c>
-      <c r="L17" s="3">
-        <v>5800</v>
-      </c>
-      <c r="M17" s="3">
-        <v>6400</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1100</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>12000</v>
-      </c>
-      <c r="E18" s="3">
-        <v>8700</v>
+        <v>6200</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F18" s="3">
-        <v>10800</v>
+        <v>4300</v>
       </c>
       <c r="G18" s="3">
-        <v>8900</v>
+        <v>-400</v>
       </c>
       <c r="H18" s="3">
-        <v>11200</v>
+        <v>9100</v>
       </c>
       <c r="I18" s="3">
-        <v>12400</v>
+        <v>12800</v>
       </c>
       <c r="J18" s="3">
+        <v>10400</v>
+      </c>
+      <c r="K18" s="3">
         <v>13800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>12800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>14100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>500</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1343,106 +1376,110 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>4800</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-8600</v>
+        <v>4600</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F20" s="3">
-        <v>-19400</v>
+        <v>3600</v>
       </c>
       <c r="G20" s="3">
-        <v>-300</v>
+        <v>7400</v>
       </c>
       <c r="H20" s="3">
-        <v>1100</v>
+        <v>-800</v>
       </c>
       <c r="I20" s="3">
-        <v>-2200</v>
+        <v>500</v>
       </c>
       <c r="J20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-10200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1600</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>16700</v>
+        <v>1600</v>
       </c>
       <c r="E21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F21" s="3">
-        <v>-8500</v>
+        <v>700</v>
       </c>
       <c r="G21" s="3">
-        <v>8600</v>
+        <v>-7700</v>
       </c>
       <c r="H21" s="3">
+        <v>9800</v>
+      </c>
+      <c r="I21" s="3">
         <v>12300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
+        <v>8900</v>
+      </c>
+      <c r="K21" s="3">
+        <v>3600</v>
+      </c>
+      <c r="L21" s="3">
+        <v>11600</v>
+      </c>
+      <c r="M21" s="3">
+        <v>11500</v>
+      </c>
+      <c r="N21" s="3">
         <v>10200</v>
       </c>
-      <c r="J21" s="3">
-        <v>3600</v>
-      </c>
-      <c r="K21" s="3">
-        <v>11600</v>
-      </c>
-      <c r="L21" s="3">
-        <v>11500</v>
-      </c>
-      <c r="M21" s="3">
-        <v>10200</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7100</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1461,31 +1498,34 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1520,108 +1560,114 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>16700</v>
-      </c>
-      <c r="E23" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="3">
         <v>100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>8600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>12300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>11600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>11500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>10200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2100</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>300</v>
-      </c>
-      <c r="E24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
-      </c>
-      <c r="F24" s="3">
-        <v>700</v>
       </c>
       <c r="G24" s="3">
         <v>700</v>
       </c>
       <c r="H24" s="3">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="I24" s="3">
         <v>200</v>
       </c>
       <c r="J24" s="3">
+        <v>200</v>
+      </c>
+      <c r="K24" s="3">
         <v>700</v>
-      </c>
-      <c r="K24" s="3">
-        <v>200</v>
       </c>
       <c r="L24" s="3">
         <v>200</v>
       </c>
       <c r="M24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1638,8 +1684,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1697,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>16400</v>
-      </c>
-      <c r="E26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="3">
         <v>-100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>8000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>12100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>10000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>11500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>11400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>10200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2100</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>16400</v>
-      </c>
-      <c r="E27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="3">
         <v>-100</v>
       </c>
-      <c r="F27" s="3">
-        <v>-9200</v>
-      </c>
       <c r="G27" s="3">
-        <v>8000</v>
+        <v>-9300</v>
       </c>
       <c r="H27" s="3">
-        <v>12100</v>
+        <v>7900</v>
       </c>
       <c r="I27" s="3">
+        <v>12000</v>
+      </c>
+      <c r="J27" s="3">
         <v>10000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>11500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>11400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>10200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2100</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1874,13 +1932,16 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -1933,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1992,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,126 +2118,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="E32" s="3">
-        <v>8600</v>
+        <v>-4600</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F32" s="3">
-        <v>19400</v>
+        <v>-3600</v>
       </c>
       <c r="G32" s="3">
-        <v>300</v>
+        <v>-7400</v>
       </c>
       <c r="H32" s="3">
-        <v>-1100</v>
+        <v>800</v>
       </c>
       <c r="I32" s="3">
-        <v>2200</v>
+        <v>-500</v>
       </c>
       <c r="J32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="K32" s="3">
         <v>10200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1600</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>16400</v>
-      </c>
-      <c r="E33" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="3">
         <v>-100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>8000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>12100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>10000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>11500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>11400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>10200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2100</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2228,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>16400</v>
-      </c>
-      <c r="E35" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="3">
         <v>-100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>8000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>12100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>10000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>11500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>11400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>10200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2100</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2374,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2397,67 +2483,71 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>122200</v>
+      </c>
+      <c r="E41" s="3">
         <v>170300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>82300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>121600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>73200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>82100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>80600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>140400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>36300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>45600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>63600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>109200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>70000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>124600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>126800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>31200</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2515,31 +2605,34 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>244000</v>
       </c>
       <c r="E43" s="3">
-        <v>5700</v>
+        <v>287000</v>
       </c>
       <c r="F43" s="3">
-        <v>1800</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>393600</v>
+      </c>
+      <c r="G43" s="3">
+        <v>344300</v>
+      </c>
+      <c r="H43" s="3">
+        <v>370400</v>
+      </c>
+      <c r="I43" s="3">
+        <v>371200</v>
+      </c>
+      <c r="J43" s="3">
+        <v>366800</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -2547,8 +2640,8 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2568,37 +2661,40 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
+      <c r="T43" s="3">
+        <v>0</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2633,34 +2729,37 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
         <v>700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I45" s="3">
+        <v>700</v>
+      </c>
+      <c r="J45" s="3">
+        <v>400</v>
+      </c>
+      <c r="K45" s="3">
         <v>500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>700</v>
-      </c>
-      <c r="I45" s="3">
-        <v>400</v>
-      </c>
-      <c r="J45" s="3">
-        <v>500</v>
-      </c>
-      <c r="K45" s="3">
-        <v>600</v>
       </c>
       <c r="L45" s="3">
         <v>600</v>
@@ -2669,54 +2768,57 @@
         <v>600</v>
       </c>
       <c r="N45" s="3">
+        <v>600</v>
+      </c>
+      <c r="O45" s="3">
         <v>900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>800</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>366600</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>458000</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>476400</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>466600</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>445100</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>454000</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>447800</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2743,98 +2845,104 @@
         <v>0</v>
       </c>
       <c r="S46" s="3">
+        <v>0</v>
+      </c>
+      <c r="T46" s="3">
         <v>32100</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>287000</v>
-      </c>
-      <c r="E47" s="3">
-        <v>387900</v>
-      </c>
-      <c r="F47" s="3">
-        <v>342400</v>
-      </c>
-      <c r="G47" s="3">
-        <v>370400</v>
-      </c>
-      <c r="H47" s="3">
-        <v>371200</v>
-      </c>
-      <c r="I47" s="3">
-        <v>366800</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>378300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>434400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>413100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>389800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>354700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>233500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>153700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>93600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>84300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>50700</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -2869,8 +2977,11 @@
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2928,8 +3039,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,31 +3163,34 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3105,8 +3225,11 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,67 +3287,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>366600</v>
+      </c>
+      <c r="E54" s="3">
         <v>458000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>476400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>466600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>445100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>454000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>447800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>519200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>471300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>459300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>454100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>464800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>303900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>278500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>221500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>94000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>82700</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,81 +3399,85 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>800</v>
       </c>
-      <c r="H57" s="3">
-        <v>1300</v>
-      </c>
       <c r="I57" s="3">
+        <v>9300</v>
+      </c>
+      <c r="J57" s="3">
         <v>1600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>100</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>42000</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -3387,90 +3521,96 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>53800</v>
+        <v>7400</v>
       </c>
       <c r="E59" s="3">
-        <v>76600</v>
+        <v>13200</v>
       </c>
       <c r="F59" s="3">
-        <v>57700</v>
+        <v>9900</v>
       </c>
       <c r="G59" s="3">
-        <v>17500</v>
+        <v>10000</v>
       </c>
       <c r="H59" s="3">
-        <v>24400</v>
+        <v>10000</v>
       </c>
       <c r="I59" s="3">
-        <v>20200</v>
+        <v>10100</v>
       </c>
       <c r="J59" s="3">
+        <v>12100</v>
+      </c>
+      <c r="K59" s="3">
         <v>81400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>25100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>22700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>18700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>93000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>28300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1700</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>72100</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>55400</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>77600</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>58500</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>18500</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>26000</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>22400</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -3497,55 +3637,58 @@
         <v>0</v>
       </c>
       <c r="S60" s="3">
+        <v>0</v>
+      </c>
+      <c r="T60" s="3">
         <v>1900</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>88500</v>
+      </c>
+      <c r="E61" s="3">
         <v>88300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>88200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>88000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>87900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>87700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>87600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>97100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>97000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>96800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>96700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>96600</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3564,67 +3707,73 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>200</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>100</v>
-      </c>
-      <c r="G62" s="3">
-        <v>200</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
+        <v>800</v>
+      </c>
+      <c r="L62" s="3">
+        <v>700</v>
+      </c>
+      <c r="M62" s="3">
+        <v>600</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>500</v>
+      </c>
+      <c r="R62" s="3">
         <v>300</v>
       </c>
-      <c r="I62" s="3">
-        <v>600</v>
-      </c>
-      <c r="J62" s="3">
-        <v>800</v>
-      </c>
-      <c r="K62" s="3">
-        <v>700</v>
-      </c>
-      <c r="L62" s="3">
-        <v>600</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3">
-        <v>700</v>
-      </c>
-      <c r="P62" s="3">
-        <v>500</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>300</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
+      <c r="T62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,67 +3955,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>160600</v>
+      </c>
+      <c r="E66" s="3">
         <v>143700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>165800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>146500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>106300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>113700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>110000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>180100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>123900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>121100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>117600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>191800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>29500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1900</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4059,8 +4227,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,67 +4289,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-42400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-36500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-39900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-30000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-10900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-9100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-11400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-10000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2100</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,67 +4537,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>206100</v>
+      </c>
+      <c r="E76" s="3">
         <v>314300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>310600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>320100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>338800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>340300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>337900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>339100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>347400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>338200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>336500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>273100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>274400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>268500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>216300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>91600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>80900</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>16400</v>
-      </c>
-      <c r="E81" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" s="3">
         <v>-100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>8000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>12100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>10000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>11500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>11400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>10200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2100</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,31 +4816,32 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -4677,8 +4876,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,67 +5186,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>10300</v>
-      </c>
-      <c r="E89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3">
         <v>6400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6200</v>
       </c>
-      <c r="G89" s="3">
-        <v>5500</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3">
         <v>5100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>12200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-100</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,31 +5274,32 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -5113,8 +5334,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,67 +5458,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>113000</v>
-      </c>
-      <c r="E94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3">
         <v>-53900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>10000</v>
       </c>
-      <c r="G94" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3">
         <v>8000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>15000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>52200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-19400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-19100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-30000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-127000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-59800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-54800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-31800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-600</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,56 +5546,57 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>-9900</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-9800</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-9800</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-9800</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-11500</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K96" s="3">
         <v>-11400</v>
       </c>
-      <c r="J96" s="3">
-        <v>-11400</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-11100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-10900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-8200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-7100</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2200</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -5372,8 +5606,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,90 +5792,96 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>-35300</v>
-      </c>
-      <c r="E100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3">
         <v>8200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>32200</v>
       </c>
-      <c r="G100" s="3">
-        <v>-9800</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3">
         <v>-11700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-79100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>48000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-9500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-20200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>164300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>5000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>47500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>121700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>8600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>31900</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5667,63 +5916,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-39300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>48400</v>
       </c>
-      <c r="G102" s="3">
-        <v>-8900</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>1500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-59800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>104100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-9300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-18000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-45600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>39300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-54600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>117200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-21600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>31200</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AFCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFCG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="92">
   <si>
     <t>AFCG</t>
   </si>
@@ -656,164 +656,170 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E8" s="3">
         <v>8700</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3">
         <v>9800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I8" s="3">
+        <v>14200</v>
+      </c>
+      <c r="J8" s="3">
+        <v>17700</v>
+      </c>
+      <c r="K8" s="3">
+        <v>16100</v>
+      </c>
+      <c r="L8" s="3">
+        <v>19700</v>
+      </c>
+      <c r="M8" s="3">
+        <v>18100</v>
+      </c>
+      <c r="N8" s="3">
+        <v>19900</v>
+      </c>
+      <c r="O8" s="3">
+        <v>17400</v>
+      </c>
+      <c r="P8" s="3">
+        <v>13000</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>11000</v>
+      </c>
+      <c r="R8" s="3">
+        <v>8700</v>
+      </c>
+      <c r="S8" s="3">
+        <v>4700</v>
+      </c>
+      <c r="T8" s="3">
         <v>4000</v>
       </c>
-      <c r="H8" s="3">
-        <v>14200</v>
-      </c>
-      <c r="I8" s="3">
-        <v>17700</v>
-      </c>
-      <c r="J8" s="3">
-        <v>16100</v>
-      </c>
-      <c r="K8" s="3">
-        <v>19700</v>
-      </c>
-      <c r="L8" s="3">
-        <v>18100</v>
-      </c>
-      <c r="M8" s="3">
-        <v>19900</v>
-      </c>
-      <c r="N8" s="3">
-        <v>17400</v>
-      </c>
-      <c r="O8" s="3">
-        <v>13000</v>
-      </c>
-      <c r="P8" s="3">
-        <v>11000</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>8700</v>
-      </c>
-      <c r="R8" s="3">
-        <v>4700</v>
-      </c>
-      <c r="S8" s="3">
-        <v>4000</v>
-      </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1600</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -838,106 +844,112 @@
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3">
         <v>3900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>100</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E10" s="3">
         <v>8700</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3">
         <v>9800</v>
       </c>
-      <c r="G10" s="3">
-        <v>4000</v>
-      </c>
       <c r="H10" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I10" s="3">
         <v>14200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>17700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>16100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>15800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>14300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>15700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>13600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>10200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>8500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6600</v>
-      </c>
-      <c r="R10" s="3">
-        <v>3800</v>
       </c>
       <c r="S10" s="3">
         <v>3800</v>
       </c>
       <c r="T10" s="3">
+        <v>3800</v>
+      </c>
+      <c r="U10" s="3">
         <v>1500</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,8 +972,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1022,8 +1035,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,35 +1100,38 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>600</v>
       </c>
-      <c r="G14" s="3">
-        <v>800</v>
-      </c>
       <c r="H14" s="3">
+        <v>100</v>
+      </c>
+      <c r="I14" s="3">
         <v>1200</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>-1300</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1128,8 +1147,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1146,8 +1165,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1208,8 +1230,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1254,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E17" s="3">
         <v>2500</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F17" s="3">
+      <c r="F17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3">
         <v>5500</v>
       </c>
-      <c r="G17" s="3">
-        <v>4400</v>
-      </c>
       <c r="H17" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I17" s="3">
         <v>5200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1100</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E18" s="3">
         <v>6200</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3">
         <v>4300</v>
       </c>
-      <c r="G18" s="3">
-        <v>-400</v>
-      </c>
       <c r="H18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="I18" s="3">
         <v>9100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>12800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>10400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>13800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>12800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>14100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>500</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,112 +1409,116 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3">
         <v>4600</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3">
         <v>3600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>7400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-10200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1600</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E21" s="3">
         <v>1600</v>
       </c>
-      <c r="E21" s="3">
-        <v>0</v>
-      </c>
       <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
         <v>700</v>
       </c>
-      <c r="G21" s="3">
-        <v>-7700</v>
-      </c>
       <c r="H21" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="I21" s="3">
         <v>9800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>12300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>11600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>11500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>10200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7100</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1501,8 +1537,11 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1527,8 +1566,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1563,114 +1602,120 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E23" s="3">
         <v>1600</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F23" s="3">
+      <c r="F23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3">
         <v>100</v>
       </c>
-      <c r="G23" s="3">
-        <v>-8500</v>
-      </c>
       <c r="H23" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="I23" s="3">
         <v>8600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>12300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>10200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>11600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>11500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>10200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2100</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3">
         <v>200</v>
-      </c>
-      <c r="G24" s="3">
-        <v>700</v>
       </c>
       <c r="H24" s="3">
         <v>700</v>
       </c>
       <c r="I24" s="3">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="J24" s="3">
         <v>200</v>
       </c>
       <c r="K24" s="3">
+        <v>200</v>
+      </c>
+      <c r="L24" s="3">
         <v>700</v>
-      </c>
-      <c r="L24" s="3">
-        <v>200</v>
       </c>
       <c r="M24" s="3">
         <v>200</v>
       </c>
       <c r="N24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -1687,8 +1732,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1797,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1200</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="F26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="3">
         <v>-100</v>
       </c>
-      <c r="G26" s="3">
-        <v>-9200</v>
-      </c>
       <c r="H26" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="I26" s="3">
         <v>8000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>12100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>11500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>11400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>10200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2100</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E27" s="3">
         <v>1200</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3">
         <v>-100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>12000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>10000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>11500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>11400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>10200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>7900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2100</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,17 +1992,20 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>200</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
@@ -1953,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
@@ -1997,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,132 +2187,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4600</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3">
         <v>-3600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-7400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>10200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1600</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1400</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="F33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="3">
         <v>-100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>8000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>12100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>10000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>11500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>11400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>10200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2100</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2382,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1400</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="F35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="3">
         <v>-100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>8000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>12100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>10000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>11500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>11400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>10200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2100</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,70 +2569,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>103600</v>
+      </c>
+      <c r="E41" s="3">
         <v>122200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>170300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>82300</v>
       </c>
-      <c r="G41" s="3">
-        <v>121600</v>
-      </c>
       <c r="H41" s="3">
+        <v>90400</v>
+      </c>
+      <c r="I41" s="3">
         <v>73200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>82100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>80600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>140400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>36300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>45600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>63600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>109200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>70000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>124600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>126800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>31200</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2608,43 +2697,46 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>297200</v>
+      </c>
+      <c r="E43" s="3">
         <v>244000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>287000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>393600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>344300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>370400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>371200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>366800</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -2664,14 +2756,17 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
+      <c r="U43" s="3">
+        <v>0</v>
       </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2696,8 +2791,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2732,37 +2827,40 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
+        <v>31900</v>
+      </c>
+      <c r="I45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J45" s="3">
         <v>700</v>
       </c>
-      <c r="H45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>700</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>500</v>
-      </c>
-      <c r="L45" s="3">
-        <v>600</v>
       </c>
       <c r="M45" s="3">
         <v>600</v>
@@ -2771,58 +2869,61 @@
         <v>600</v>
       </c>
       <c r="O45" s="3">
+        <v>600</v>
+      </c>
+      <c r="P45" s="3">
         <v>900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>800</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>402100</v>
+      </c>
+      <c r="E46" s="3">
         <v>366600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>458000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>476400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>466600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>445100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>454000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>447800</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2848,16 +2949,19 @@
         <v>0</v>
       </c>
       <c r="T46" s="3">
+        <v>0</v>
+      </c>
+      <c r="U46" s="3">
         <v>32100</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2882,44 +2986,47 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>378300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>434400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>413100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>389800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>354700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>233500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>153700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>93600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>84300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>50700</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2944,8 +3051,8 @@
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -2980,8 +3087,11 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3042,8 +3152,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,8 +3282,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3192,8 +3311,8 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -3228,8 +3347,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,70 +3412,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>402100</v>
+      </c>
+      <c r="E54" s="3">
         <v>366600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>458000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>476400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>466600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>445100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>454000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>447800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>519200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>471300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>459300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>454100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>464800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>303900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>278500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>221500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>94000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>82700</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,88 +3529,92 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>500</v>
+      </c>
+      <c r="E57" s="3">
         <v>700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>100</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E58" s="3">
         <v>60000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>35000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>60000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>42000</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
@@ -3524,97 +3657,103 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E59" s="3">
         <v>7400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>13200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
+        <v>9900</v>
+      </c>
+      <c r="I59" s="3">
         <v>10000</v>
       </c>
-      <c r="H59" s="3">
-        <v>10000</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>81400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>25100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>22700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>18700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>93000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>28300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1700</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>112100</v>
+      </c>
+      <c r="E60" s="3">
         <v>72100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>55400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>77600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>58500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>26000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>22400</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -3640,58 +3779,61 @@
         <v>0</v>
       </c>
       <c r="T60" s="3">
+        <v>0</v>
+      </c>
+      <c r="U60" s="3">
         <v>1900</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>88600</v>
+      </c>
+      <c r="E61" s="3">
         <v>88500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>88300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>88200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>88000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>87900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>87700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>87600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>97100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>97000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>96800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>96700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>96600</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3710,8 +3852,11 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3727,8 +3872,8 @@
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
+      <c r="H62" s="3">
+        <v>0</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -3736,44 +3881,47 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>600</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
         <v>700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>300</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,70 +4112,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>200700</v>
+      </c>
+      <c r="E66" s="3">
         <v>160600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>143700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>165800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>146500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>106300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>113700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>110000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>180100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>123900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>121100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>117600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>191800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>29500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1900</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,70 +4462,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-50700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-42400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-36500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-39900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-30000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-10900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-9100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-11400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-10000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2100</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,70 +4722,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>201400</v>
+      </c>
+      <c r="E76" s="3">
         <v>206100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>314300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>310600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>320100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>338800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>340300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>337900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>339100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>347400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>338200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>336500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>273100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>274400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>268500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>216300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>91600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>80900</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4852,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1400</v>
       </c>
-      <c r="E81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="F81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G81" s="3">
         <v>-100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>8000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>12100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>10000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>11500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>11400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>10200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2100</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,8 +5014,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4843,8 +5041,8 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -4879,8 +5077,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5402,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>2200</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3">
         <v>6400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6200</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3">
         <v>5100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>12200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>10600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-100</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,8 +5494,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5301,8 +5521,8 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -5337,8 +5557,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,70 +5687,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-56900</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3">
         <v>-53900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>10000</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3">
         <v>8000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>15000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>52200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-19400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-19100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-30000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-127000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-59800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-54800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-31800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-600</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,8 +5779,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5573,33 +5806,33 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3">
         <v>-11400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-11100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-10900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-8200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-7100</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-5100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2200</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
@@ -5609,8 +5842,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,70 +6037,76 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>36200</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3">
         <v>8200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>32200</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
         <v>-11700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-79100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>48000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-9500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-20200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>164300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>5000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>47500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>121700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>8600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>31900</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5883,8 +6131,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -5919,66 +6167,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-18600</v>
       </c>
       <c r="E102" s="3">
         <v>0</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-39300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>48400</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>1500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-59800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>104100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-18000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-45600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>39300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-54600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>117200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-21600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>31200</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AFCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFCG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
   <si>
     <t>AFCG</t>
   </si>
@@ -656,170 +656,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E8" s="3">
         <v>2300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8700</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="3">
-        <v>9800</v>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H8" s="3">
+        <v>7800</v>
+      </c>
+      <c r="I8" s="3">
         <v>3800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>14200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>17700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>17400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>13000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1600</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -847,109 +854,115 @@
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3">
         <v>3900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>100</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E10" s="3">
         <v>2300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8700</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3">
-        <v>9800</v>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H10" s="3">
+        <v>7800</v>
+      </c>
+      <c r="I10" s="3">
         <v>3800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>14200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>17700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>16100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>15800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>14300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>15700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>13600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>10200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>8500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6600</v>
-      </c>
-      <c r="S10" s="3">
-        <v>3800</v>
       </c>
       <c r="T10" s="3">
         <v>3800</v>
       </c>
       <c r="U10" s="3">
+        <v>3800</v>
+      </c>
+      <c r="V10" s="3">
         <v>1500</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -973,8 +986,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1038,8 +1052,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1103,38 +1120,41 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>600</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
         <v>100</v>
       </c>
       <c r="I14" s="3">
+        <v>100</v>
+      </c>
+      <c r="J14" s="3">
         <v>1200</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>-1300</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1150,8 +1170,8 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1168,8 +1188,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1233,8 +1256,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1255,138 +1281,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E17" s="3">
         <v>3500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2500</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="G17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="3">
         <v>5500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1100</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6200</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G18" s="3">
-        <v>4300</v>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H18" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I18" s="3">
         <v>-1300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>9100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>12800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>13800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>12800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>11000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>8500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>5700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>500</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1410,118 +1443,122 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>700</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4600</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
         <v>3600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>7400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-10200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1600</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1600</v>
       </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
       <c r="G21" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="I21" s="3">
         <v>-8700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>12300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>11600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>11500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>10200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7100</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1540,8 +1577,11 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1569,8 +1609,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1605,120 +1645,126 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1600</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G23" s="3">
-        <v>100</v>
+      <c r="G23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I23" s="3">
         <v>-8800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>12300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>10200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>11600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>11500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>10200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2100</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
         <v>200</v>
-      </c>
-      <c r="H24" s="3">
-        <v>700</v>
       </c>
       <c r="I24" s="3">
         <v>700</v>
       </c>
       <c r="J24" s="3">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="K24" s="3">
         <v>200</v>
       </c>
       <c r="L24" s="3">
+        <v>200</v>
+      </c>
+      <c r="M24" s="3">
         <v>700</v>
-      </c>
-      <c r="M24" s="3">
-        <v>200</v>
       </c>
       <c r="N24" s="3">
         <v>200</v>
       </c>
       <c r="O24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
@@ -1735,8 +1781,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1800,138 +1849,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1200</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-100</v>
+      <c r="G26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I26" s="3">
         <v>-9400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>12100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>11500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>11400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>10200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2100</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1200</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="G27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H27" s="3">
         <v>-100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>12000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>10000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>11500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>11400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>10200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>7000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>7900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2100</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1995,8 +2053,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2004,20 +2065,20 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>200</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I29" s="3">
         <v>200</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
@@ -2060,8 +2121,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2125,8 +2189,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2190,138 +2257,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4600</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
         <v>-3600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-7400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>10200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1600</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1400</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="G33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H33" s="3">
         <v>-100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>12100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>10000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>11500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>11400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>10200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2100</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2385,143 +2461,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1400</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="G35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" s="3">
         <v>-100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>12100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>10000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>11500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>11400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>10200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2100</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2545,8 +2630,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2570,73 +2656,77 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E41" s="3">
         <v>103600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>122200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>170300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>82300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>90400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>73200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>82100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>80600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>140400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>36300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>45600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>63600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>109200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>70000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>124600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>126800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>31200</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2700,46 +2790,49 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>307000</v>
+      </c>
+      <c r="E43" s="3">
         <v>297200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>244000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>287000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>393600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>344300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>370400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>371200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>366800</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -2759,14 +2852,17 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
+      <c r="V43" s="3">
+        <v>0</v>
       </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2794,8 +2890,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2830,40 +2926,43 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E45" s="3">
         <v>1200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>31900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>500</v>
-      </c>
-      <c r="M45" s="3">
-        <v>600</v>
       </c>
       <c r="N45" s="3">
         <v>600</v>
@@ -2872,61 +2971,64 @@
         <v>600</v>
       </c>
       <c r="P45" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q45" s="3">
         <v>900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>800</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>321700</v>
+      </c>
+      <c r="E46" s="3">
         <v>402100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>366600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>458000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>476400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>466600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>445100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>454000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>447800</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2952,16 +3054,19 @@
         <v>0</v>
       </c>
       <c r="U46" s="3">
+        <v>0</v>
+      </c>
+      <c r="V46" s="3">
         <v>32100</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2989,44 +3094,47 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>378300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>434400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>413100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>389800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>354700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>233500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>153700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>93600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>84300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>50700</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3054,8 +3162,8 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -3090,8 +3198,11 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3155,8 +3266,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3220,8 +3334,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3285,8 +3402,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3314,8 +3434,8 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -3350,8 +3470,11 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3415,73 +3538,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>321700</v>
+      </c>
+      <c r="E54" s="3">
         <v>402100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>366600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>458000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>476400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>466600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>445100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>454000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>447800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>519200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>471300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>459300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>454100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>464800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>303900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>278500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>221500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>94000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>82700</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3505,8 +3634,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3530,94 +3660,98 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>800</v>
+      </c>
+      <c r="E57" s="3">
         <v>500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>100</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E58" s="3">
         <v>100000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>60000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>35000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>60000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>42000</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -3660,103 +3794,109 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E59" s="3">
         <v>7500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13200</v>
-      </c>
-      <c r="G59" s="3">
-        <v>9900</v>
       </c>
       <c r="H59" s="3">
         <v>9900</v>
       </c>
       <c r="I59" s="3">
+        <v>9900</v>
+      </c>
+      <c r="J59" s="3">
         <v>10000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>81400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>25100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>22700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>18700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>93000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>28300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1700</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E60" s="3">
         <v>112100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>72100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>55400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>77600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>58500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>18500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>26000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>22400</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -3782,61 +3922,64 @@
         <v>0</v>
       </c>
       <c r="U60" s="3">
+        <v>0</v>
+      </c>
+      <c r="V60" s="3">
         <v>1900</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>88800</v>
+      </c>
+      <c r="E61" s="3">
         <v>88600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>88500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>88300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>88200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>88000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>87900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>87700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>87600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>97100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>97000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>96800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>96700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>96600</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3855,8 +3998,11 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3872,11 +4018,11 @@
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
@@ -3884,44 +4030,47 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>600</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3">
         <v>700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>300</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3985,8 +4134,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4050,8 +4202,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4115,73 +4270,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>120900</v>
+      </c>
+      <c r="E66" s="3">
         <v>200700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>160600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>143700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>165800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>146500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>106300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>113700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>110000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>180100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>123900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>121100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>117600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>191800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>29500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1900</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4205,8 +4366,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4270,8 +4432,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4335,8 +4500,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4400,8 +4568,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4465,73 +4636,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-51800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-50700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-42400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-36500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-39900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-30000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-10900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-9100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-11400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-10000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2100</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4595,8 +4772,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4660,8 +4840,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4725,73 +4908,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>200800</v>
+      </c>
+      <c r="E76" s="3">
         <v>201400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>206100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>314300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>310600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>320100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>338800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>340300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>337900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>339100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>347400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>338200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>336500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>273100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>274400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>268500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>216300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>91600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>80900</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4855,143 +5044,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1400</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="G81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H81" s="3">
         <v>-100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>12100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>10000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>11500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>11400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>10200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2100</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5015,8 +5213,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5044,8 +5243,8 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -5080,8 +5279,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5145,8 +5347,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5210,8 +5415,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5275,8 +5483,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5340,8 +5551,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5405,73 +5619,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E89" s="3">
         <v>2200</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3">
         <v>6400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6200</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3">
         <v>5100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>12200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>10600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-100</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5495,8 +5715,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5524,8 +5745,8 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -5560,8 +5781,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5625,8 +5849,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5690,73 +5917,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-56900</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3">
         <v>-53900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>10000</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3">
         <v>8000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>15000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>52200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-19400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-19100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-30000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-127000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-59800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-54800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-31800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-600</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5780,8 +6013,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5809,33 +6043,33 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M96" s="3">
         <v>-11400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-11100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-10900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-8200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-5100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-2200</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -5845,8 +6079,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5910,8 +6147,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5975,8 +6215,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6040,73 +6283,79 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-85100</v>
+      </c>
+      <c r="E100" s="3">
         <v>36200</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3">
         <v>8200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>32200</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
         <v>-11700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-79100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>48000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-9500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-20200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>164300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>5000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>47500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>121700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>8600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>31900</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6134,8 +6383,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6170,69 +6419,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-18600</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
         <v>0</v>
       </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-39300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>48400</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>1500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-59800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>104100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-9300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-18000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-45600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>39300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-54600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>117200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-21600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>31200</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AFCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFCG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="92">
   <si>
     <t>AFCG</t>
   </si>
@@ -656,177 +656,184 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
         <v>7300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8700</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H8" s="3">
+        <v>22700</v>
+      </c>
+      <c r="I8" s="3">
         <v>7800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>14200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>17700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>16100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>18100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>19900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>17400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1600</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -857,112 +864,118 @@
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3">
         <v>3900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>100</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E10" s="3">
         <v>7300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8700</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H10" s="3">
+        <v>22700</v>
+      </c>
+      <c r="I10" s="3">
         <v>7800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>14200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>17700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>16100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>15800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>14300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>15700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>13600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>10200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>8500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6600</v>
-      </c>
-      <c r="T10" s="3">
-        <v>3800</v>
       </c>
       <c r="U10" s="3">
         <v>3800</v>
       </c>
       <c r="V10" s="3">
+        <v>3800</v>
+      </c>
+      <c r="W10" s="3">
         <v>1500</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -987,8 +1000,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1055,8 +1069,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1123,41 +1140,44 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
-        <v>100</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
         <v>100</v>
       </c>
       <c r="J14" s="3">
+        <v>100</v>
+      </c>
+      <c r="K14" s="3">
         <v>1200</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>-1300</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1173,8 +1193,8 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1191,8 +1211,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1259,8 +1282,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1282,144 +1308,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E17" s="3">
         <v>2500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2500</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="I17" s="3">
         <v>5500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1100</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6200</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H18" s="3">
+        <v>16900</v>
+      </c>
+      <c r="I18" s="3">
         <v>2300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>12800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>13800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>12800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>14100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>11000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>8500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>5700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>500</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1444,124 +1477,128 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E20" s="3">
         <v>700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4600</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I20" s="3">
         <v>3600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>7400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-10200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1600</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E21" s="3">
         <v>4200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1600</v>
       </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
       <c r="H21" s="3">
+        <v>15500</v>
+      </c>
+      <c r="I21" s="3">
         <v>-1300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-8700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>12300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>11600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>11500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>10200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>7100</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1580,8 +1617,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1612,8 +1652,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1648,126 +1688,132 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E23" s="3">
         <v>4200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1600</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H23" s="3">
+        <v>15500</v>
+      </c>
+      <c r="I23" s="3">
         <v>-1400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>12300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>10200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>11600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>11500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>10200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2100</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H24" s="3">
+        <v>300</v>
+      </c>
+      <c r="I24" s="3">
         <v>200</v>
-      </c>
-      <c r="I24" s="3">
-        <v>700</v>
       </c>
       <c r="J24" s="3">
         <v>700</v>
       </c>
       <c r="K24" s="3">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="L24" s="3">
         <v>200</v>
       </c>
       <c r="M24" s="3">
+        <v>200</v>
+      </c>
+      <c r="N24" s="3">
         <v>700</v>
-      </c>
-      <c r="N24" s="3">
-        <v>200</v>
       </c>
       <c r="O24" s="3">
         <v>200</v>
       </c>
       <c r="P24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -1784,8 +1830,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1852,144 +1901,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E26" s="3">
         <v>4100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1200</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H26" s="3">
+        <v>15200</v>
+      </c>
+      <c r="I26" s="3">
         <v>-1600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>12100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>11500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>11400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>10200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>7900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2100</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E27" s="3">
         <v>4000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1200</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H27" s="3">
+        <v>16300</v>
+      </c>
+      <c r="I27" s="3">
         <v>-100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>12000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>10000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>11500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>11400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>10200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>7000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>7900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2100</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2056,8 +2114,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2068,20 +2129,20 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>200</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I29" s="3">
         <v>1500</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>200</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
@@ -2124,8 +2185,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2192,8 +2256,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2260,144 +2327,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4600</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I32" s="3">
         <v>-3600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-7400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>10200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1600</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E33" s="3">
         <v>4100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1400</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H33" s="3">
+        <v>16400</v>
+      </c>
+      <c r="I33" s="3">
         <v>-100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>12100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>10000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>11500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>11400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>10200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2100</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2464,149 +2540,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E35" s="3">
         <v>4100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1400</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H35" s="3">
+        <v>16400</v>
+      </c>
+      <c r="I35" s="3">
         <v>-100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>12100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>10000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>11500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>11400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>10200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2100</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2631,8 +2716,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2657,76 +2743,80 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E41" s="3">
         <v>3300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>103600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>122200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>170300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>82300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>90400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>73200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>82100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>80600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>140400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>36300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>45600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>63600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>109200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>70000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>124600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>126800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>31200</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2793,49 +2883,52 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>285500</v>
+      </c>
+      <c r="E43" s="3">
         <v>307000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>297200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>244000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>287000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>393600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>344300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>370400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>371200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>366800</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -2855,14 +2948,17 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
+      <c r="W43" s="3">
+        <v>0</v>
       </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2893,8 +2989,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2929,43 +3025,46 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E45" s="3">
         <v>11300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>31900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>500</v>
-      </c>
-      <c r="N45" s="3">
-        <v>600</v>
       </c>
       <c r="O45" s="3">
         <v>600</v>
@@ -2974,64 +3073,67 @@
         <v>600</v>
       </c>
       <c r="Q45" s="3">
+        <v>600</v>
+      </c>
+      <c r="R45" s="3">
         <v>900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>800</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>290600</v>
+      </c>
+      <c r="E46" s="3">
         <v>321700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>402100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>366600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>458000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>476400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>466600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>445100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>454000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>447800</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -3057,16 +3159,19 @@
         <v>0</v>
       </c>
       <c r="V46" s="3">
+        <v>0</v>
+      </c>
+      <c r="W46" s="3">
         <v>32100</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3097,44 +3202,47 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
         <v>378300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>434400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>413100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>389800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>354700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>233500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>153700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>93600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>84300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>50700</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3165,8 +3273,8 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -3201,8 +3309,11 @@
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3269,8 +3380,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3337,8 +3451,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3405,8 +3522,11 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3437,8 +3557,8 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -3473,8 +3593,11 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3541,76 +3664,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>290600</v>
+      </c>
+      <c r="E54" s="3">
         <v>321700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>402100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>366600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>458000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>476400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>466600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>445100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>454000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>447800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>519200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>471300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>459300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>454100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>464800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>303900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>278500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>221500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>94000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>82700</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3635,8 +3764,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3661,100 +3791,104 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>700</v>
+      </c>
+      <c r="E57" s="3">
         <v>800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>100</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E58" s="3">
         <v>22300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>100000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>60000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>35000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>60000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>42000</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -3797,109 +3931,115 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E59" s="3">
         <v>5300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13200</v>
-      </c>
-      <c r="H59" s="3">
-        <v>9900</v>
       </c>
       <c r="I59" s="3">
         <v>9900</v>
       </c>
       <c r="J59" s="3">
+        <v>9900</v>
+      </c>
+      <c r="K59" s="3">
         <v>10000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>81400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>25100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>22700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>93000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>28300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1700</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E60" s="3">
         <v>32100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>112100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>72100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>55400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>77600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>58500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>18500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22400</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -3925,64 +4065,67 @@
         <v>0</v>
       </c>
       <c r="V60" s="3">
+        <v>0</v>
+      </c>
+      <c r="W60" s="3">
         <v>1900</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>88900</v>
+      </c>
+      <c r="E61" s="3">
         <v>88800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>88600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>88500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>88300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>88200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>88000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>87900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>87700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>87600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>97100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>97000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>96800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>96700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>96600</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4001,8 +4144,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4021,11 +4167,11 @@
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3">
+        <v>0</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -4033,44 +4179,47 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
         <v>800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>600</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3">
         <v>700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>300</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
+      <c r="W62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4137,8 +4286,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4205,8 +4357,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4273,76 +4428,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>105900</v>
+      </c>
+      <c r="E66" s="3">
         <v>120900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>200700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>160600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>143700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>165800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>146500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>106300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>113700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>110000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>180100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>123900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>121100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>117600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>191800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>29500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1900</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4367,8 +4528,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4435,8 +4597,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4503,8 +4668,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4571,8 +4739,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4639,76 +4810,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-68400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-51800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-50700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-42400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-36500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-39900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-30000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-10900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-9100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-11400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-10000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2100</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4775,8 +4952,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4843,8 +5023,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4911,76 +5094,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>184700</v>
+      </c>
+      <c r="E76" s="3">
         <v>200800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>201400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>206100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>314300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>310600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>320100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>338800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>340300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>337900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>339100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>347400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>338200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>336500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>273100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>274400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>268500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>216300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>91600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>80900</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5047,149 +5236,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E81" s="3">
         <v>4100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1400</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H81" s="3">
+        <v>16400</v>
+      </c>
+      <c r="I81" s="3">
         <v>-100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>12100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>10000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>11500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>11400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>10200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2100</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5214,8 +5412,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5246,8 +5445,8 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -5282,8 +5481,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5350,8 +5552,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5418,8 +5623,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5486,8 +5694,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5554,8 +5765,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5622,76 +5836,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E89" s="3">
         <v>3900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2200</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H89" s="3">
+        <v>10300</v>
+      </c>
+      <c r="I89" s="3">
         <v>6400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6200</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3">
         <v>5100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>12200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>10600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>5100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-100</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5716,8 +5936,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5748,8 +5969,8 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -5784,8 +6005,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5852,8 +6076,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5920,76 +6147,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-19100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-56900</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H94" s="3">
+        <v>113000</v>
+      </c>
+      <c r="I94" s="3">
         <v>-53900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>10000</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
         <v>8000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>15000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>52200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-19400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-19100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-30000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-127000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-59800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-54800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-31800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-600</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6014,8 +6247,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6046,33 +6280,33 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N96" s="3">
         <v>-11400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-11100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-10900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-7100</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-5100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-2200</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -6082,8 +6316,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6150,8 +6387,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6218,8 +6458,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6286,76 +6529,82 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-85100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>36200</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H100" s="3">
+        <v>-35300</v>
+      </c>
+      <c r="I100" s="3">
         <v>8200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>32200</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>-11700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-79100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>48000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-9500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-20200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>164300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>5000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>47500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>121700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>8600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>31900</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6386,8 +6635,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6422,72 +6671,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-100300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-18600</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
         <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>88000</v>
+      </c>
+      <c r="I102" s="3">
         <v>-39300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>48400</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>1500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-59800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>104100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-9300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-18000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-45600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>39300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-54600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>117200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-21600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>31200</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AFCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFCG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="92">
   <si>
     <t>AFCG</t>
   </si>
@@ -656,191 +656,197 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>5100</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3">
         <v>7300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>22700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>19700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>18100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>19900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>17400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>13000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1600</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -877,118 +883,124 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3">
         <v>3900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>100</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E10" s="3">
         <v>-800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-9600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>8700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>22700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>14200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>17700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>16100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>15800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>14300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>15700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>13600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>10200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>8500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>6600</v>
-      </c>
-      <c r="V10" s="3">
-        <v>3800</v>
       </c>
       <c r="W10" s="3">
         <v>3800</v>
       </c>
       <c r="X10" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Y10" s="3">
         <v>1500</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1015,8 +1027,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1089,8 +1102,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,13 +1179,16 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>-400</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1177,33 +1196,33 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
-        <v>100</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>100</v>
       </c>
       <c r="L14" s="3">
+        <v>100</v>
+      </c>
+      <c r="M14" s="3">
         <v>1200</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>-1300</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1219,8 +1238,8 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1237,8 +1256,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1311,8 +1333,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1361,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E17" s="3">
         <v>2200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1100</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-12000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>16900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>12800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>12800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>14100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>11000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>8500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>500</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,136 +1544,140 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E20" s="3">
         <v>10300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>7400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-10200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1600</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-13400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-13300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>15500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>12300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>11600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>11500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>10200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>7100</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1660,8 +1696,11 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1698,8 +1737,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1734,138 +1773,144 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-13400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-13300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>15500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>12300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>10200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>11600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>11500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>10200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>7900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2100</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
-      </c>
-      <c r="K24" s="3">
-        <v>700</v>
       </c>
       <c r="L24" s="3">
         <v>700</v>
       </c>
       <c r="M24" s="3">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="N24" s="3">
         <v>200</v>
       </c>
       <c r="O24" s="3">
+        <v>200</v>
+      </c>
+      <c r="P24" s="3">
         <v>700</v>
-      </c>
-      <c r="P24" s="3">
-        <v>200</v>
       </c>
       <c r="Q24" s="3">
         <v>200</v>
       </c>
       <c r="R24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -1882,8 +1927,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2004,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-13200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>15200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>8000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>12100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>10000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>11500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>11400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>10200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>7000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>7900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2100</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-13300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>16300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>12000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>10000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>11500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>11400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>10200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>7000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>7900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2100</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2235,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2196,20 +2256,20 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>200</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>1200</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>1500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>200</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
@@ -2252,8 +2312,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2389,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,156 +2466,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-10300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-7400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>10200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-13200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>16400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>8000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>12100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>10000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>11500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>11400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>10200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>7000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>7900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2100</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2697,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-13200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>16400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>8000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>12100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>10000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>11500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>11400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>10200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>7000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>7900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2100</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2887,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,82 +2916,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E41" s="3">
         <v>45100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>103600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>122200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>170300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>82300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>90400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>73200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>82100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>80600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>140400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>36300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>45600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>63600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>109200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>70000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>124600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>126800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>31200</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2979,55 +3068,58 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>234500</v>
+      </c>
+      <c r="E43" s="3">
         <v>241300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>285500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>307000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>297200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>244000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>287000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>393600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>344300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>370400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>371200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>366800</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
@@ -3047,14 +3139,17 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
+      <c r="Y43" s="3">
+        <v>0</v>
       </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3091,8 +3186,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3127,49 +3222,52 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E45" s="3">
         <v>2300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>11300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>31900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
-      </c>
-      <c r="P45" s="3">
-        <v>600</v>
       </c>
       <c r="Q45" s="3">
         <v>600</v>
@@ -3178,70 +3276,73 @@
         <v>600</v>
       </c>
       <c r="S45" s="3">
+        <v>600</v>
+      </c>
+      <c r="T45" s="3">
         <v>900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>800</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>275600</v>
+      </c>
+      <c r="E46" s="3">
         <v>288700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>290600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>321700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>402100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>366600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>458000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>476400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>466600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>445100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>454000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>447800</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -3267,16 +3368,19 @@
         <v>0</v>
       </c>
       <c r="X46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
         <v>32100</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3313,44 +3417,47 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3">
         <v>378300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>434400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>413100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>389800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>354700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>233500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>153700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>93600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>84300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>50700</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3387,8 +3494,8 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
@@ -3423,8 +3530,11 @@
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3497,8 +3607,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3684,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,8 +3761,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3683,8 +3802,8 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -3719,8 +3838,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,82 +3915,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>275600</v>
+      </c>
+      <c r="E54" s="3">
         <v>288700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>290600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>321700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>402100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>366600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>458000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>476400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>466600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>445100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>454000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>447800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>519200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>471300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>459300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>454100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>464800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>303900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>278500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>221500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>94000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>82700</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4023,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,112 +4052,116 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>800</v>
+      </c>
+      <c r="E57" s="3">
         <v>1100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>100</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E58" s="3">
         <v>22000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>22300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>100000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>60000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>35000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>60000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>42000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4071,121 +4204,127 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>100</v>
+      </c>
+      <c r="E59" s="3">
         <v>3600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13200</v>
-      </c>
-      <c r="J59" s="3">
-        <v>9900</v>
       </c>
       <c r="K59" s="3">
         <v>9900</v>
       </c>
       <c r="L59" s="3">
+        <v>9900</v>
+      </c>
+      <c r="M59" s="3">
         <v>10000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>81400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>25100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>22700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>93000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>28300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1700</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E60" s="3">
         <v>30300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>17000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>112100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>72100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>55400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>77600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>58500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>22400</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -4211,70 +4350,73 @@
         <v>0</v>
       </c>
       <c r="X60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="3">
         <v>1900</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>76300</v>
+      </c>
+      <c r="E61" s="3">
         <v>89100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>88900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>88800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>88600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>88500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>88300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>88200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>88000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>87900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>87700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>87600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>97100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>97000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>96800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>96700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>96600</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4293,8 +4435,11 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4319,11 +4464,11 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
+        <v>0</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
@@ -4331,44 +4476,47 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3">
         <v>800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>600</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T62" s="3">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U62" s="3">
         <v>700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>300</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4589,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4666,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,82 +4743,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E66" s="3">
         <v>119400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>105900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>120900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>200700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>160600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>143700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>165800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>146500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>106300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>113700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>110000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>180100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>123900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>121100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>117600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>191800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>29500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1900</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4851,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4926,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5003,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4913,8 +5080,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,82 +5157,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-83400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-84300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-68400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-51800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-50700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-42400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-36500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-39900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-30000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-10900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-9100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-11400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-10000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2100</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5311,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5388,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,82 +5465,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>175600</v>
+      </c>
+      <c r="E76" s="3">
         <v>169300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>184700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>200800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>201400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>206100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>314300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>310600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>320100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>338800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>340300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>337900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>339100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>347400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>338200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>336500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>273100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>274400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>268500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>216300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>91600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>80900</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5619,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-13200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>16400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>8000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>12100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>10000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>11500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>11400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>10200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>7000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>7900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2100</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,8 +5809,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5650,8 +5848,8 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -5686,8 +5884,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5961,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6038,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6115,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6192,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,82 +6269,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E89" s="3">
         <v>6100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>10300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6200</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3">
         <v>5100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>12200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>10600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>5100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-100</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,8 +6377,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6196,8 +6416,8 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -6232,8 +6452,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6529,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,82 +6606,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E94" s="3">
         <v>27400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>15500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-19100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-56900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>113000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-53900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>10000</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
         <v>8000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>15000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>52200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-19400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-19100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-30000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-127000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-59800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-54800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-31800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-600</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6714,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6520,33 +6753,33 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3">
         <v>-11400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-11100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-10900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-8200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-7100</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-5100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-2200</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -6556,8 +6789,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6866,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6943,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,82 +7020,88 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E100" s="3">
         <v>8200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-17200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-85100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>36200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-43800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-35300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>8200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>32200</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>-11700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-79100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>48000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-9500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-20200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>164300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>5000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>47500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>121700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>8600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>31900</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6890,8 +7138,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -6926,78 +7174,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E102" s="3">
         <v>41700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-100300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-18600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-48100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>88000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-39300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>48400</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>1500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-59800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>104100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-18000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-45600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>39300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-54600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>117200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-21600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>31200</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AFCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFCG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="92">
   <si>
     <t>AFCG</t>
   </si>
@@ -656,197 +656,204 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E8" s="3">
         <v>5100</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
         <v>7300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>22700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>16100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>19700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>18100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>19900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>17400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>13000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1600</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -886,121 +893,127 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3">
         <v>3900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>100</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E10" s="3">
         <v>5100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-9600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>22700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>14200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>17700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>16100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>15800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>14300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>15700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>13600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>10200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>8500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>6600</v>
-      </c>
-      <c r="W10" s="3">
-        <v>3800</v>
       </c>
       <c r="X10" s="3">
         <v>3800</v>
       </c>
       <c r="Y10" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Z10" s="3">
         <v>1500</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1028,8 +1041,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1105,8 +1119,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1182,50 +1199,53 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E14" s="3">
         <v>-400</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>100</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>100</v>
       </c>
       <c r="M14" s="3">
+        <v>100</v>
+      </c>
+      <c r="N14" s="3">
         <v>1200</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>-1300</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1241,8 +1261,8 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1259,8 +1279,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1336,8 +1359,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1362,162 +1388,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E17" s="3">
         <v>7400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1100</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-12000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>16900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>12800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>12800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>14100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>11000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>8500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>500</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1545,142 +1578,146 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>10300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1600</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E21" s="3">
         <v>800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-13400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-13300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>15500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>12300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>11600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>11500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>10200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>7100</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1699,8 +1736,11 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1740,8 +1780,8 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1776,144 +1816,150 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E23" s="3">
         <v>1200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-13400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-13300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>15500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>12300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>10200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>11600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>11500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>10200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>7100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>7900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2100</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
-      </c>
-      <c r="L24" s="3">
-        <v>700</v>
       </c>
       <c r="M24" s="3">
         <v>700</v>
       </c>
       <c r="N24" s="3">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="O24" s="3">
         <v>200</v>
       </c>
       <c r="P24" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q24" s="3">
         <v>700</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>200</v>
       </c>
       <c r="R24" s="3">
         <v>200</v>
       </c>
       <c r="S24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -1930,8 +1976,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2007,162 +2056,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E26" s="3">
         <v>900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-13200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>15200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>8000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>12100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>10000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>11500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>11400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>10200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>7000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>7900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2100</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E27" s="3">
         <v>800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-13300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>16300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>12000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>10000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>11500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>11400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>10200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>7000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>7900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2100</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2238,8 +2296,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2259,20 +2320,20 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>200</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>1200</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>1500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>200</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
@@ -2315,8 +2376,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2392,8 +2456,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2469,162 +2536,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>3100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-10300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>10200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E33" s="3">
         <v>900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-13200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>16400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>8000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>12100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>10000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>11500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>11400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>10200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>7000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>7900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2100</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2700,167 +2776,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E35" s="3">
         <v>900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-13200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>16400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>8000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>12100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>10000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>11500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>11400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>10200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>7000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>7900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2100</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2888,8 +2973,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2917,85 +3003,89 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>112700</v>
+      </c>
+      <c r="E41" s="3">
         <v>38600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>45100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>103600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>122200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>170300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>82300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>90400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>73200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>82100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>80600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>140400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>36300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>45600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>63600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>109200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>70000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>124600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>126800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>31200</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3071,58 +3161,61 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E43" s="3">
         <v>234500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>241300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>285500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>307000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>297200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>244000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>287000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>393600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>344300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>370400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>371200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>366800</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
@@ -3142,14 +3235,17 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>3</v>
+      <c r="Z43" s="3">
+        <v>0</v>
       </c>
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3189,8 +3285,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3225,52 +3321,55 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E45" s="3">
         <v>2400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>31900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>500</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>600</v>
       </c>
       <c r="R45" s="3">
         <v>600</v>
@@ -3279,73 +3378,76 @@
         <v>600</v>
       </c>
       <c r="T45" s="3">
+        <v>600</v>
+      </c>
+      <c r="U45" s="3">
         <v>900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>800</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>115600</v>
+      </c>
+      <c r="E46" s="3">
         <v>275600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>288700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>290600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>321700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>402100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>366600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>458000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>476400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>466600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>445100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>454000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>447800</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -3371,21 +3473,24 @@
         <v>0</v>
       </c>
       <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="3">
         <v>32100</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>279200</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>3</v>
@@ -3420,44 +3525,47 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3">
         <v>378300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>434400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>413100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>389800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>354700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>233500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>153700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>93600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>84300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>50700</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3497,8 +3605,8 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
+      <c r="P48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
@@ -3533,8 +3641,11 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3610,8 +3721,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3687,8 +3801,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3764,8 +3881,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3805,8 +3925,8 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -3841,8 +3961,11 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3918,85 +4041,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>394900</v>
+      </c>
+      <c r="E54" s="3">
         <v>275600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>288700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>290600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>321700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>402100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>366600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>458000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>476400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>466600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>445100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>454000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>447800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>519200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>471300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>459300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>454100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>464800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>303900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>278500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>221500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>94000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>82700</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4024,8 +4153,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4053,8 +4183,9 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4062,109 +4193,112 @@
         <v>800</v>
       </c>
       <c r="E57" s="3">
+        <v>800</v>
+      </c>
+      <c r="F57" s="3">
         <v>1100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>100</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>126000</v>
+      </c>
+      <c r="E58" s="3">
         <v>21000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>22000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>22300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>100000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>60000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>35000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>60000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>42000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4207,127 +4341,133 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E59" s="3">
         <v>100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13200</v>
-      </c>
-      <c r="K59" s="3">
-        <v>9900</v>
       </c>
       <c r="L59" s="3">
         <v>9900</v>
       </c>
       <c r="M59" s="3">
+        <v>9900</v>
+      </c>
+      <c r="N59" s="3">
         <v>10000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>81400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>25100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>22700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>18700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>93000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>28300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>8200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1700</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>132600</v>
+      </c>
+      <c r="E60" s="3">
         <v>23700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>30300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>32100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>112100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>72100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>55400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>77600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>58500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>18500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>26000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>22400</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -4353,73 +4493,76 @@
         <v>0</v>
       </c>
       <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="3">
         <v>1900</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>76400</v>
+      </c>
+      <c r="E61" s="3">
         <v>76300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>89100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>88900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>88800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>88600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>88500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>88300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>88200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>88000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>87900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>87700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>87600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>97100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>97000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>96800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>96700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>96600</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4438,8 +4581,11 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4467,11 +4613,11 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
+        <v>0</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
@@ -4479,44 +4625,47 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
         <v>800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>600</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U62" s="3">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3">
         <v>700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>300</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z62" s="3">
-        <v>0</v>
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4592,8 +4741,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4669,8 +4821,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4746,85 +4901,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>209100</v>
+      </c>
+      <c r="E66" s="3">
         <v>100000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>119400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>105900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>120900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>200700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>160600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>143700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>165800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>146500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>106300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>113700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>110000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>180100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>123900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>121100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>117600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>191800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>29500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>10100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1900</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4852,8 +5013,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4929,8 +5091,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5006,8 +5171,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5083,8 +5251,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5160,85 +5331,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-73100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-83400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-84300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-68400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-51800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-50700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-42400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-36500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-39900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-30000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-10900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-9100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-11400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2100</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5314,8 +5491,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5391,8 +5571,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5468,85 +5651,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>185800</v>
+      </c>
+      <c r="E76" s="3">
         <v>175600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>169300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>184700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>200800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>201400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>206100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>314300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>310600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>320100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>338800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>340300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>337900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>339100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>347400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>338200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>336500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>273100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>274400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>268500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>216300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>91600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>80900</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5622,167 +5811,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E81" s="3">
         <v>900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-13200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>16400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>8000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>12100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>10000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>11500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>11400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>10200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>7000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>7900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2100</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5810,8 +6008,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5851,8 +6050,8 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -5887,8 +6086,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5964,8 +6166,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6041,8 +6246,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6118,8 +6326,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6195,8 +6406,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6272,85 +6486,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-30800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6200</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3">
         <v>5100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>12200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>10600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>5100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-100</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6378,8 +6598,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6419,8 +6640,8 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -6455,8 +6676,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6532,8 +6756,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6609,85 +6836,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3">
         <v>11100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>27400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>15500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-19100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-56900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>113000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-53900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>10000</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
         <v>8000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>15000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>52200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-19400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-19100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-30000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-127000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-59800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-54800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-31800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-600</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6715,8 +6948,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6732,8 +6966,8 @@
       <c r="G96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>3</v>
+      <c r="H96" s="3">
+        <v>7400</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>3</v>
@@ -6756,33 +6990,33 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-11100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-10900</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-8200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-7100</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-5100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-2200</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -6792,8 +7026,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6869,8 +7106,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6946,8 +7186,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7023,85 +7266,91 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>105000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-17000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>8200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-17200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-85100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>36200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-43800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-35300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>8200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>32200</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
         <v>-11700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-79100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>48000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-9500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-20200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>164300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>5000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>47500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>121700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>8600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>31900</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7141,8 +7390,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -7177,81 +7426,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>74100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>41700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-100300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-18600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-48100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>88000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-39300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>48400</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>1500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-59800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>104100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-9300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-18000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-45600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>39300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-54600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>117200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-21600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>31200</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
